--- a/data/tech-debt-register.xlsx
+++ b/data/tech-debt-register.xlsx
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>57, 130, 214</t>
+          <t>25, 89, 173</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
